--- a/data/CCI.xlsx
+++ b/data/CCI.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4222DE5B-E1A8-4C3D-B227-4367266DA199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="251">
   <si>
     <t>ICD10 code</t>
   </si>
@@ -779,19 +788,17 @@
   </si>
   <si>
     <t>M35.3</t>
+  </si>
+  <si>
+    <t>得分</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -800,17 +807,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF0645AD"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FF202122"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -819,56 +819,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -876,105 +827,26 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAECF0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -984,192 +856,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1178,337 +870,54 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFA2A9B1"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFA2A9B1"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFA2A9B1"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFA2A9B1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1758,1906 +1167,2531 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B232"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C232"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="52.25" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" ht="14.25" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:2">
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:2">
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:2">
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:2">
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:2">
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:2">
+      <c r="C8" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:2">
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:2">
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:2">
+      <c r="C11" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:2">
+      <c r="C12" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:2">
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
+      <c r="C14" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:2">
+      <c r="C15" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:2">
+      <c r="C16" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:2">
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:2">
+      <c r="C18" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:2">
+      <c r="C19" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" ht="14.25" spans="1:2">
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" ht="14.25" spans="1:2">
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:2">
+      <c r="C22" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="C23" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" ht="14.25" spans="1:2">
+      <c r="C24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" ht="14.25" spans="1:2">
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" ht="14.25" spans="1:2">
+      <c r="C26" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="C27" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="C28" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:2">
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" ht="14.25" spans="1:2">
+      <c r="C31" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" ht="14.25" spans="1:2">
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" ht="14.25" spans="1:2">
+      <c r="C33" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:2">
+      <c r="C34" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:2">
+      <c r="C35" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:2">
+      <c r="C36" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:2">
+      <c r="C37" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:2">
+      <c r="C38" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:2">
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" ht="14.25" spans="1:2">
+      <c r="C40" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" ht="14.25" spans="1:2">
+      <c r="C41" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" ht="14.25" spans="1:2">
+      <c r="C42" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" ht="14.25" spans="1:2">
+      <c r="C43" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" ht="14.25" spans="1:2">
+      <c r="C44" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" ht="14.25" spans="1:2">
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" ht="14.25" spans="1:2">
+      <c r="C46" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
+      <c r="C47" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" ht="14.25" spans="1:2">
+      <c r="C48" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" ht="14.25" spans="1:2">
+      <c r="C49" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" ht="14.25" spans="1:2">
+      <c r="C50" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" ht="14.25" spans="1:2">
+      <c r="C51" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" ht="14.25" spans="1:2">
+      <c r="C52" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" ht="14.25" spans="1:2">
+      <c r="C53" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:2">
+      <c r="C54" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" ht="14.25" spans="1:2">
+      <c r="C55" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" ht="14.25" spans="1:2">
+      <c r="C56" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" ht="14.25" spans="1:2">
+      <c r="C57" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" ht="14.25" spans="1:2">
+      <c r="C58" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" ht="14.25" spans="1:2">
+      <c r="C59" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" ht="14.25" spans="1:2">
+      <c r="C60" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" ht="14.25" spans="1:2">
+      <c r="C61" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" ht="14.25" spans="1:2">
+      <c r="C62" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" ht="14.25" spans="1:2">
+      <c r="C63" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" ht="14.25" spans="1:2">
+      <c r="C64" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" ht="14.25" spans="1:2">
+      <c r="C65" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" ht="14.25" spans="1:2">
+      <c r="C66" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" ht="14.25" spans="1:2">
+      <c r="C67" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" ht="14.25" spans="1:2">
+      <c r="C68" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" ht="14.25" spans="1:2">
+      <c r="C69" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" ht="14.25" spans="1:2">
+      <c r="C70" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" ht="14.25" spans="1:2">
+      <c r="C71" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" ht="14.25" spans="1:2">
+      <c r="C72" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" ht="14.25" spans="1:2">
+      <c r="C73" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:2">
+      <c r="C74" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" ht="14.25" spans="1:2">
+      <c r="C75" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" ht="14.25" spans="1:2">
+      <c r="C76" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:2">
+      <c r="C77" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" ht="14.25" spans="1:2">
+      <c r="C78" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="80" spans="1:2">
+      <c r="C79" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="81" ht="14.25" spans="1:2">
+      <c r="C80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="82" spans="1:2">
+      <c r="C81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="83" spans="1:2">
+      <c r="C82" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:2">
+      <c r="C83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="85" ht="14.25" spans="1:2">
+      <c r="C84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="86" ht="14.25" spans="1:2">
+      <c r="C85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="87" ht="14.25" spans="1:2">
+      <c r="C86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="88" spans="1:2">
+      <c r="C87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="89" ht="14.25" spans="1:2">
+      <c r="C88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="90" ht="14.25" spans="1:2">
+      <c r="C89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="91" spans="1:2">
+      <c r="C90" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="92" ht="14.25" spans="1:2">
+      <c r="C91" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="93" ht="14.25" spans="1:2">
+      <c r="C92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="94" spans="1:2">
+      <c r="C93" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
+      <c r="C94" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="96" ht="14.25" spans="1:2">
+      <c r="C95" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="97" spans="1:2">
+      <c r="C96" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="98" ht="14.25" spans="1:2">
+      <c r="C97" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="99" spans="1:2">
+      <c r="C98" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" ht="14.25" spans="1:2">
+      <c r="C99" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="101" ht="14.25" spans="1:2">
+      <c r="C100" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="102" ht="14.25" spans="1:2">
+      <c r="C101" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="103" ht="14.25" spans="1:2">
+      <c r="C102" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="104" ht="14.25" spans="1:2">
+      <c r="C103" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="105" ht="14.25" spans="1:2">
+      <c r="C104" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="106" spans="1:2">
+      <c r="C105" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="107" ht="14.25" spans="1:2">
+      <c r="C106" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="108" ht="14.25" spans="1:2">
+      <c r="C107" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="109" ht="14.25" spans="1:2">
+      <c r="C108" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="110" ht="14.25" spans="1:2">
+      <c r="C109" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="111" spans="1:2">
+      <c r="C110" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="112" spans="1:2">
+      <c r="C111" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="113" spans="1:2">
+      <c r="C112" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="114" ht="14.25" spans="1:2">
+      <c r="C113" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="115" spans="1:2">
+      <c r="C114" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="116" ht="14.25" spans="1:2">
+      <c r="C115" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="117" ht="14.25" spans="1:2">
+      <c r="C116" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="118" spans="1:2">
+      <c r="C117" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="119" ht="14.25" spans="1:2">
+      <c r="C118" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="120" spans="1:2">
+      <c r="C119" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="121" ht="14.25" spans="1:2">
+      <c r="C120" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="122" ht="14.25" spans="1:2">
+      <c r="C121" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="123" ht="14.25" spans="1:2">
+      <c r="C122" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="124" ht="14.25" spans="1:2">
+      <c r="C123" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="125" ht="14.25" spans="1:2">
+      <c r="C124" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="126" ht="14.25" spans="1:2">
+      <c r="C125" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="127" ht="14.25" spans="1:2">
+      <c r="C126" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
+      <c r="C127" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="129" spans="1:2">
+      <c r="C128" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="130" spans="1:2">
+      <c r="C129" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="131" spans="1:2">
+      <c r="C130" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="132" spans="1:2">
+      <c r="C131" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="133" spans="1:2">
+      <c r="C132" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
+      <c r="C133" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
+      <c r="C134" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="136" ht="14.25" spans="1:2">
+      <c r="C135" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="137" spans="1:2">
+      <c r="C136" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="138" spans="1:2">
+      <c r="C137" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="139" spans="1:2">
+      <c r="C138" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="140" spans="1:2">
+      <c r="C139" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="141" ht="14.25" spans="1:2">
+      <c r="C140" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="142" ht="14.25" spans="1:2">
+      <c r="C141" s="4"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="143" ht="14.25" spans="1:2">
+      <c r="C142" s="4"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="144" ht="14.25" spans="1:2">
+      <c r="C143" s="4"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="145" spans="1:2">
+      <c r="C144" s="4"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="146" spans="1:2">
+      <c r="C145" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="147" spans="1:2">
+      <c r="C146" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="148" spans="1:2">
+      <c r="C147" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="149" spans="1:2">
+      <c r="C148" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>159</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="150" spans="1:2">
+      <c r="C149" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="151" spans="1:2">
+      <c r="C150" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>161</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="152" spans="1:2">
+      <c r="C151" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>162</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="153" spans="1:2">
+      <c r="C152" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="154" spans="1:2">
+      <c r="C153" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="155" spans="1:2">
+      <c r="C154" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>165</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="156" spans="1:2">
+      <c r="C155" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="157" ht="14.25" spans="1:2">
+      <c r="C156" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="158" ht="14.25" spans="1:2">
+      <c r="C157" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="159" ht="14.25" spans="1:2">
+      <c r="C158" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="160" ht="14.25" spans="1:2">
+      <c r="C159" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>171</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="161" ht="14.25" spans="1:2">
+      <c r="C160" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="162" ht="14.25" spans="1:2">
+      <c r="C161" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="163" spans="1:2">
+      <c r="C162" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="164" ht="14.25" spans="1:2">
+      <c r="C163" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="165" ht="14.25" spans="1:2">
+      <c r="C164" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="166" ht="14.25" spans="1:2">
+      <c r="C165" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>177</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="167" ht="14.25" spans="1:2">
+      <c r="C166" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="168" ht="14.25" spans="1:2">
+      <c r="C167" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>179</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="169" ht="14.25" spans="1:2">
+      <c r="C168" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>180</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="170" ht="14.25" spans="1:2">
+      <c r="C169" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="171" ht="14.25" spans="1:2">
+      <c r="C170" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>182</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="172" ht="14.25" spans="1:2">
+      <c r="C171" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>183</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="173" ht="14.25" spans="1:2">
+      <c r="C172" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="174" ht="14.25" spans="1:2">
+      <c r="C173" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>186</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="175" ht="14.25" spans="1:2">
+      <c r="C174" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="176" ht="14.25" spans="1:2">
+      <c r="C175" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>188</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="177" spans="1:2">
+      <c r="C176" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>189</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="178" spans="1:2">
+      <c r="C177" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>190</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="179" spans="1:2">
+      <c r="C178" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="180" spans="1:2">
+      <c r="C179" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>192</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="181" spans="1:2">
+      <c r="C180" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="182" ht="14.25" spans="1:2">
+      <c r="C181" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>194</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="183" ht="14.25" spans="1:2">
+      <c r="C182" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="184" ht="14.25" spans="1:2">
+      <c r="C183" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>196</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="185" spans="1:2">
+      <c r="C184" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="186" spans="1:2">
+      <c r="C185" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="187" ht="14.25" spans="1:2">
+      <c r="C186" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>200</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="188" ht="14.25" spans="1:2">
+      <c r="C187" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>201</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="189" ht="14.25" spans="1:2">
+      <c r="C188" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>202</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="190" ht="14.25" spans="1:2">
+      <c r="C189" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>204</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="191" ht="14.25" spans="1:2">
+      <c r="C190" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="192" ht="14.25" spans="1:2">
+      <c r="C191" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>206</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="193" ht="14.25" spans="1:2">
+      <c r="C192" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>207</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="194" ht="14.25" spans="1:2">
+      <c r="C193" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>208</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="195" ht="14.25" spans="1:2">
+      <c r="C194" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>209</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="196" ht="14.25" spans="1:2">
+      <c r="C195" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="197" ht="14.25" spans="1:2">
+      <c r="C196" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>211</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="198" ht="14.25" spans="1:2">
+      <c r="C197" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="199" ht="14.25" spans="1:2">
+      <c r="C198" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>214</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="200" ht="14.25" spans="1:2">
+      <c r="C199" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="201" ht="14.25" spans="1:2">
+      <c r="C200" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="202" ht="14.25" spans="1:2">
+      <c r="C201" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="203" ht="14.25" spans="1:2">
+      <c r="C202" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>218</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="204" ht="14.25" spans="1:2">
+      <c r="C203" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>219</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="205" ht="14.25" spans="1:2">
+      <c r="C204" s="4"/>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>221</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="206" ht="14.25" spans="1:2">
+      <c r="C205" s="4"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>222</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="207" ht="14.25" spans="1:2">
+      <c r="C206" s="4"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="208" ht="14.25" spans="1:2">
+      <c r="C207" s="4"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>224</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="209" ht="14.25" spans="1:2">
+      <c r="C208" s="4"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>225</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="210" ht="14.25" spans="1:2">
+      <c r="C209" s="4"/>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>226</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="211" spans="1:2">
+      <c r="C210" s="4"/>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>227</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="212" spans="1:2">
+      <c r="C211" s="4"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>228</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="213" spans="1:2">
+      <c r="C212" s="4"/>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>229</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="214" spans="1:2">
+      <c r="C213" s="4"/>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>230</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="215" spans="1:2">
+      <c r="C214" s="4"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>231</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="216" spans="1:2">
+      <c r="C215" s="4"/>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="217" spans="1:2">
+      <c r="C216" s="4"/>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>233</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="218" ht="14.25" spans="1:2">
+      <c r="C217" s="4"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>234</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="219" ht="14.25" spans="1:2">
+      <c r="C218" s="4"/>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>235</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="220" ht="14.25" spans="1:2">
+      <c r="C219" s="4"/>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="221" ht="14.25" spans="1:2">
+      <c r="C220" s="4"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>237</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="222" ht="14.25" spans="1:2">
+      <c r="C221" s="4"/>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>238</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="223" ht="14.25" spans="1:2">
+      <c r="C222" s="4"/>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="224" ht="14.25" spans="1:2">
+      <c r="C223" s="4"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>240</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="225" ht="14.25" spans="1:2">
+      <c r="C224" s="4"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>242</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="226" spans="1:2">
+      <c r="C225" s="4"/>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>243</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="227" ht="14.25" spans="1:2">
+      <c r="C226" s="4"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>244</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="228" ht="14.25" spans="1:2">
+      <c r="C227" s="4"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>245</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="229" ht="14.25" spans="1:2">
+      <c r="C228" s="4"/>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>246</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="230" spans="1:2">
+      <c r="C229" s="4"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>247</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="231" ht="14.25" spans="1:2">
+      <c r="C230" s="4"/>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>248</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="232" ht="14.25" spans="1:2">
+      <c r="C231" s="4"/>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>241</v>
       </c>
+      <c r="C232" s="4"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="ICD10 code" tooltip="https://ccmdb.kuality.ca/index.php?title=Property:Charlson_ICD10Code"/>
-    <hyperlink ref="B1" r:id="rId2" display="Charlson component" tooltip="https://ccmdb.kuality.ca/index.php?title=Property:Charlson_component"/>
-  </hyperlinks>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>